--- a/docs/PX案件チェックシート_北広島町川小田.xlsx
+++ b/docs/PX案件チェックシート_北広島町川小田.xlsx
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>空きあり=良／要確認=注意／空きなし・不明=リスク。マップは申込ベースで埋まるため最新性に注意。 / 【最大リスク】最寄：芸北変電所 約4.1km（110kV／空容量0／N-1電制 不可♯3／出力制御あり）＝社内スコアリングDBのゲート条件（空容量≦0かつN-1電制不可＝上位系増強リスク）に該当し「除外」ランク。次点の下山変電所 約6.1kmも同条件で除外。総合17点（Cランク）。接続検討前に中国電力ネットワークへ空容量の最新状況と増強見通しを必ずヒアリングすること。</t>
+          <t>空きあり=良／要確認=注意／空きなし・不明=リスク。マップは申込ベースで埋まるため最新性に注意。 / 最寄：芸北変電所 約4.1km（110kV／二次6kV×2台・22kV×1台／空容量0／N-1電制 不可♯3／出力制御あり）。社内スコアリングDB(2026-08-18)のゲート条件（空容量≦0かつN-1電制不可）に該当し「除外」ランク・総合17点。次点の下山変電所 約6.1kmも同条件。ただし下記No.2のとおり中国電力NWの蓄電池接続検討の回答実績では芸北系に増強回答なし。公表空容量は特高側の値のため、高圧連系の可否は接続検討で確認が必要。※芸北変電所の座標はGoogle Places名称一致による推定のため距離は目安。</t>
         </is>
       </c>
     </row>
@@ -3425,10 +3425,14 @@
           <t>先行申込案件の状況</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>芸北系＝増強回答実績なし（当該設備）</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>注意</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -3438,7 +3442,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>先着優先のため、検討中に容量を先取りされるリスクを確認。</t>
+          <t>先着優先のため、検討中に容量を先取りされるリスクを確認。 / 中国電力NW「蓄電池設備の接続検討で早期連系追加対策・系統増強が必要と回答したことのある設備」(更新2026-07-17)より。芸北変電所（広③S13-1/-2）・芸北支線（広③L20／110kV・2回線）は当該設備として早期連系追加対策・系統増強とも回答実績なし。増強が必要と回答された上位系は基幹系統の基S23-2の1件のみ。対して下山変電所（広③S12）・下山線（広③L18／110kV・1回線）は上位系に基S10-1/基S11/基S13/基L22に加え広③L10滝山川線が並び、滝山川線は当該設備として増強〇の実績あり。→ 同じ北広島町でも芸北系の方が制約が軽く、回線数（2回線）でも有利。才乙配電塔（広③H3／22-6kV）も上位系は基S23-2のみで芸北系と同一。※同資料は回答実績を示すもので連系可否を保証しない。</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3464,7 @@
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>110kV</t>
+          <t>110kV（芸北SS二次は6kV×2台）</t>
         </is>
       </c>
       <c r="E6" s="28" t="inlineStr">
@@ -3475,7 +3479,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>6.6〜33kV=良／66kV=注意／154kV以上=リスク（系統影響評価で回答が長期化）。 / 特高側は空容量0。高圧2MW連系の配電線側の空きを個別に確認。</t>
+          <t>6.6〜33kV=良／66kV=注意／154kV以上=リスク（系統影響評価で回答が長期化）。 / 芸北変電所は110/22kV×1台、110/6kV×2台。6kVバンクがあるため高圧2MW連系の受け皿自体は存在する。特高側の公表空容量は0のため、配電線側の空きを個別に確認すること。</t>
         </is>
       </c>
     </row>
@@ -3533,15 +3537,15 @@
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>注意</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>簡易=良／詳細の可能性=注意／不明=リスク。TSOへ事前ヒアリング推奨。</t>
+          <t>簡易=良／詳細の可能性=注意／不明=リスク。TSOへ事前ヒアリング推奨。 / 上位系（基S23-2）で増強回答の実績があるため、詳細検討に回る可能性を想定。中国電力NWへの事前ヒアリングを推奨。</t>
         </is>
       </c>
     </row>
